--- a/templates/填空题导入模板.xlsx
+++ b/templates/填空题导入模板.xlsx
@@ -4,14 +4,78 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="答题卡" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="使用说明" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="答题卡" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+  <si>
+    <t>填空题导入 — 答题卡制作说明</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>一、配套导入</t>
+  </si>
+  <si>
+    <t>• Word 文件：完整试卷，考试端全文展示；不要求与答题卡逐题一一对应。</t>
+  </si>
+  <si>
+    <t>• 本 Excel：答题卡，定义每空的题号、标准答案与分值。</t>
+  </si>
+  <si>
+    <t>• 可选附件：在管理台导入时单独上传，供学员下载参考。</t>
+  </si>
+  <si>
+    <t>二、工作表与表头</t>
+  </si>
+  <si>
+    <t>• 答题卡数据须写在名为「答题卡」的工作表中（本模板已创建）。</t>
+  </si>
+  <si>
+    <t>• 第 1 行为表头，列名固定为：题号、答案、分值（请勿修改列名）。</t>
+  </si>
+  <si>
+    <t>三、一行一空</t>
+  </si>
+  <si>
+    <t>• 每一行代表 Word 试卷中的一个空。</t>
+  </si>
+  <si>
+    <t>• 同一题号填写多行，表示该题有多个空；行顺序即第 1 空、第 2 空……</t>
+  </si>
+  <si>
+    <t>四、各列填写规则</t>
+  </si>
+  <si>
+    <t>• 题号：正整数；建议与 Word 中题号一致，便于学员对照。</t>
+  </si>
+  <si>
+    <t>• 答案：必填。多个可接受答案用英文竖线 | 分隔（全角 ｜ 也可）。</t>
+  </si>
+  <si>
+    <t>• 分值：非负整数。客观填空部分将按此分值自动计分。</t>
+  </si>
+  <si>
+    <t>• 答案列已设为文本格式，避免日期、前导零等被 Excel 自动改写。</t>
+  </si>
+  <si>
+    <t>五、导入前请检查</t>
+  </si>
+  <si>
+    <t>• 删除「答题卡」工作表中答案列以【示例】开头的行（模板自带示例）。</t>
+  </si>
+  <si>
+    <t>• 可参考同目录示例：填空题导入示例-题目.docx、填空题导入示例-答题卡.xlsx。</t>
+  </si>
+  <si>
+    <t>• 支持 .xls 与 .xlsx 格式。</t>
+  </si>
   <si>
     <t>题号</t>
   </si>
@@ -22,26 +86,32 @@
     <t>分值</t>
   </si>
   <si>
-    <t>示例答案A</t>
-  </si>
-  <si>
-    <t>示例答案B|别名B</t>
-  </si>
-  <si>
-    <t>第二题答案</t>
+    <t>【说明】请删除下方【示例】行后填写真实内容；详细规则见「使用说明」工作表</t>
+  </si>
+  <si>
+    <t>【示例】示例答案A</t>
+  </si>
+  <si>
+    <t>【示例】示例答案A|别名A</t>
+  </si>
+  <si>
+    <t>【示例】2020-10-17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,8 +134,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,37 +478,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="80" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" ht="8" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="8" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="9" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -443,12 +658,23 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
         <v>3</v>
       </c>
     </row>
